--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590957.8769930921</v>
+        <v>590958</v>
       </c>
       <c r="R2" t="n">
-        <v>6740147.895370704</v>
+        <v>6740148</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2001-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590957.8769930921</v>
+        <v>590958</v>
       </c>
       <c r="R3" t="n">
-        <v>6740147.895370704</v>
+        <v>6740148</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2001-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2001-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590957.8769930921</v>
+        <v>590958</v>
       </c>
       <c r="R4" t="n">
-        <v>6740147.895370704</v>
+        <v>6740148</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +965,9 @@
           <t>2001-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2001-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590969.020600846</v>
+        <v>590969</v>
       </c>
       <c r="R5" t="n">
-        <v>6740133.034141714</v>
+        <v>6740133</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,19 +1076,9 @@
           <t>2001-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2001-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590969.020600846</v>
+        <v>590969</v>
       </c>
       <c r="R6" t="n">
-        <v>6740133.034141714</v>
+        <v>6740133</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,19 +1187,9 @@
           <t>2001-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2001-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98557</v>
+        <v>98563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98597</v>
+        <v>98603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98603</v>
+        <v>98610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98614</v>
+        <v>98621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98624</v>
+        <v>98629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91461345</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>91461342</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>91461352</v>
       </c>
       <c r="B4" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>91461359</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>91461354</v>
       </c>
       <c r="B6" t="n">
-        <v>98629</v>
+        <v>98637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29544-2023 artfynd.xlsx
+++ b/artfynd/A 29544-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91461345</v>
+        <v>91461463</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+          <t>Lennåsen, SO-sluttningen 160 möh, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590958</v>
+        <v>591032</v>
       </c>
       <c r="R2" t="n">
-        <v>6740148</v>
+        <v>6740128</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
+          <t>Myr, rikkärr, sluttande fastmattekärr, backkärr, glest med låga tallar, socklar och gropar, medelrik D</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 243084N</t>
+          <t>Gst Fyndnr 242971L</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91461342</v>
+        <v>91461354</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590958</v>
+        <v>590969</v>
       </c>
       <c r="R3" t="n">
-        <v>6740148</v>
+        <v>6740133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,12 +870,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
+          <t>Skog, barrskog, bryn mot litet kärr, och bland gles tallskärm, genomsilad bergsluttning</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 243087N</t>
+          <t>Gst Fyndnr 243076N</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91461352</v>
+        <v>91461460</v>
       </c>
       <c r="B4" t="n">
-        <v>101752</v>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+          <t>Lennåsen, SO-sluttningen 160 möh, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590958</v>
+        <v>591032</v>
       </c>
       <c r="R4" t="n">
-        <v>6740148</v>
+        <v>6740128</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,12 +981,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
+          <t>Myr, rikkärr, sluttande fastmattekärr, backkärr, glest med låga tallar, socklar och gropar, medelrik D</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 243078N</t>
+          <t>Gst Fyndnr 242974L</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91461359</v>
+        <v>91461352</v>
       </c>
       <c r="B5" t="n">
-        <v>100847</v>
+        <v>102241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590969</v>
+        <v>590958</v>
       </c>
       <c r="R5" t="n">
-        <v>6740133</v>
+        <v>6740148</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skog, barrskog, bryn mot litet kärr, och bland gles tallskärm, genomsilad bergsluttning</t>
+          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 243072N</t>
+          <t>Gst Fyndnr 243078N</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91461354</v>
+        <v>91461448</v>
       </c>
       <c r="B6" t="n">
-        <v>98637</v>
+        <v>97977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221944</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+          <t>Lennåsen, SO-sluttningen 160 möh, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590969</v>
+        <v>591032</v>
       </c>
       <c r="R6" t="n">
-        <v>6740133</v>
+        <v>6740128</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,12 +1199,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skog, barrskog, bryn mot litet kärr, och bland gles tallskärm, genomsilad bergsluttning</t>
+          <t>Myr, rikkärr, sluttande fastmattekärr, backkärr, glest med låga tallar, socklar och gropar, medelrik D</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 243076N</t>
+          <t>Gst Fyndnr 242984L</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1223,6 +1219,561 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91461342</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590958</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6740148</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 243087N</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91461449</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lennåsen, SO-sluttningen 160 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591032</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6740128</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Myr, rikkärr, sluttande fastmattekärr, backkärr, glest med låga tallar, socklar och gropar, medelrik D</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 242983L</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91461462</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lennåsen, SO-sluttningen 160 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>591032</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6740128</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Myr, rikkärr, sluttande fastmattekärr, backkärr, glest med låga tallar, socklar och gropar, medelrik D</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 242972L</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91461345</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590958</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6740148</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skog, Tallskog, gles välgallrad skog i myrlänt bergsluttning, ört-rikt</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 243084N</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>91461359</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lennåsen, SO-sluttningen, 150 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590969</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6740133</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skog, barrskog, bryn mot litet kärr, och bland gles tallskärm, genomsilad bergsluttning</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 243072N</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
